--- a/Team-Data/2014-15/2-8-2014-15.xlsx
+++ b/Team-Data/2014-15/2-8-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,58 +728,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
         <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J2" t="n">
         <v>80.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L2" t="n">
         <v>9.9</v>
       </c>
       <c r="M2" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="N2" t="n">
         <v>0.391</v>
       </c>
       <c r="O2" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P2" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="S2" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="V2" t="n">
         <v>14.1</v>
@@ -730,28 +797,28 @@
         <v>18.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.5</v>
+        <v>103.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -760,13 +827,13 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN2" t="n">
         <v>1</v>
@@ -778,13 +845,13 @@
         <v>17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -799,16 +866,16 @@
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>14</v>
@@ -969,31 +1036,31 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>23</v>
@@ -1133,7 +1200,7 @@
         <v>19</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>22</v>
@@ -1148,13 +1215,13 @@
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
         <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
         <v>14</v>
@@ -1166,19 +1233,19 @@
         <v>23</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
         <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.431</v>
+        <v>0.44</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
@@ -1225,7 +1292,7 @@
         <v>35.8</v>
       </c>
       <c r="J5" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K5" t="n">
         <v>0.423</v>
@@ -1234,31 +1301,31 @@
         <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.306</v>
+        <v>0.302</v>
       </c>
       <c r="O5" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.735</v>
+        <v>0.734</v>
       </c>
       <c r="R5" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S5" t="n">
         <v>33.9</v>
       </c>
       <c r="T5" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="U5" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
         <v>11.8</v>
@@ -1267,25 +1334,25 @@
         <v>5.9</v>
       </c>
       <c r="X5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA5" t="n">
         <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="AC5" t="n">
         <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
         <v>28</v>
@@ -1327,16 +1394,16 @@
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
         <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1345,10 +1412,10 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.615</v>
+        <v>0.608</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
@@ -1407,10 +1474,10 @@
         <v>36.8</v>
       </c>
       <c r="J6" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L6" t="n">
         <v>7.7</v>
@@ -1422,61 +1489,61 @@
         <v>0.359</v>
       </c>
       <c r="O6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="P6" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S6" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="T6" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="U6" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V6" t="n">
         <v>14.2</v>
       </c>
       <c r="W6" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X6" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA6" t="n">
         <v>22</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="AC6" t="n">
         <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
         <v>5</v>
@@ -1485,7 +1552,7 @@
         <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
         <v>20</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1512,13 +1579,13 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV6" t="n">
         <v>12</v>
@@ -1530,16 +1597,16 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA6" t="n">
         <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -1571,58 +1638,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" t="n">
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J7" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.455</v>
+        <v>0.453</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M7" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.354</v>
+        <v>0.35</v>
       </c>
       <c r="O7" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P7" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.753</v>
+        <v>0.755</v>
       </c>
       <c r="R7" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S7" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="T7" t="n">
         <v>42.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V7" t="n">
         <v>13.9</v>
@@ -1631,7 +1698,7 @@
         <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y7" t="n">
         <v>4.8</v>
@@ -1640,19 +1707,19 @@
         <v>18.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
-        <v>102</v>
+        <v>101.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -1670,22 +1737,22 @@
         <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM7" t="n">
         <v>8</v>
       </c>
-      <c r="AM7" t="n">
-        <v>7</v>
-      </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>16</v>
@@ -1694,25 +1761,25 @@
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>25</v>
       </c>
       <c r="AY7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1721,7 +1788,7 @@
         <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -1753,34 +1820,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" t="n">
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.673</v>
+        <v>0.66</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
       </c>
       <c r="I8" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="J8" t="n">
-        <v>86.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="N8" t="n">
         <v>0.359</v>
@@ -1792,22 +1859,22 @@
         <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R8" t="n">
         <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W8" t="n">
         <v>8.199999999999999</v>
@@ -1822,34 +1889,34 @@
         <v>19.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>107</v>
+        <v>106.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1861,22 +1928,22 @@
         <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
         <v>21</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR8" t="n">
         <v>15</v>
       </c>
-      <c r="AR8" t="n">
-        <v>14</v>
-      </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1894,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ8" t="n">
         <v>13</v>
@@ -1906,7 +1973,7 @@
         <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2080,22 @@
         <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF9" t="n">
         <v>22</v>
       </c>
-      <c r="AF9" t="n">
-        <v>21</v>
-      </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI9" t="n">
         <v>16</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>18</v>
       </c>
       <c r="AJ9" t="n">
         <v>4</v>
@@ -2046,7 +2113,7 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
         <v>5</v>
@@ -2055,7 +2122,7 @@
         <v>22</v>
       </c>
       <c r="AR9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
@@ -2064,28 +2131,28 @@
         <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
         <v>15</v>
       </c>
       <c r="AY9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
         <v>22</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>0.385</v>
+        <v>0.392</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,16 +2202,16 @@
         <v>36.7</v>
       </c>
       <c r="J10" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.429</v>
+        <v>0.428</v>
       </c>
       <c r="L10" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N10" t="n">
         <v>0.344</v>
@@ -2156,16 +2223,16 @@
         <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.707</v>
+        <v>0.706</v>
       </c>
       <c r="R10" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="T10" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="U10" t="n">
         <v>21.4</v>
@@ -2174,16 +2241,16 @@
         <v>13.8</v>
       </c>
       <c r="W10" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X10" t="n">
         <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA10" t="n">
         <v>19.8</v>
@@ -2192,22 +2259,22 @@
         <v>98.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>22</v>
@@ -2225,7 +2292,7 @@
         <v>10</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
         <v>24</v>
@@ -2240,22 +2307,22 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2270,7 +2337,7 @@
         <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>11.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2386,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -2416,10 +2483,10 @@
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2431,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
@@ -2440,7 +2507,7 @@
         <v>2</v>
       </c>
       <c r="AY11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ11" t="n">
         <v>14</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -2484,13 +2551,13 @@
         <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,40 +2566,40 @@
         <v>36.8</v>
       </c>
       <c r="J12" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L12" t="n">
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V12" t="n">
         <v>17</v>
@@ -2541,28 +2608,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y12" t="n">
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.7</v>
+        <v>102.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
@@ -2574,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ12" t="n">
         <v>14</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2610,7 +2677,7 @@
         <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,22 +2686,22 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>0.385</v>
+        <v>0.373</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2693,16 +2760,16 @@
         <v>20.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O13" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P13" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.758</v>
+        <v>0.755</v>
       </c>
       <c r="R13" t="n">
         <v>10.7</v>
@@ -2711,19 +2778,19 @@
         <v>34.1</v>
       </c>
       <c r="T13" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U13" t="n">
         <v>21.1</v>
       </c>
       <c r="V13" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W13" t="n">
         <v>6.1</v>
       </c>
       <c r="X13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y13" t="n">
         <v>4.8</v>
@@ -2735,25 +2802,25 @@
         <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="AC13" t="n">
         <v>-1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2762,7 +2829,7 @@
         <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
         <v>22</v>
@@ -2780,7 +2847,7 @@
         <v>24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
         <v>18</v>
@@ -2801,22 +2868,22 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -2845,64 +2912,64 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E14" t="n">
         <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.635</v>
+        <v>0.647</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J14" t="n">
-        <v>83</v>
+        <v>82.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="N14" t="n">
         <v>0.374</v>
       </c>
       <c r="O14" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P14" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R14" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T14" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="U14" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V14" t="n">
         <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X14" t="n">
         <v>4.8</v>
@@ -2911,7 +2978,7 @@
         <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
         <v>21.3</v>
@@ -2920,16 +2987,16 @@
         <v>106.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>8</v>
@@ -2956,10 +3023,10 @@
         <v>5</v>
       </c>
       <c r="AO14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
         <v>23</v>
@@ -2968,7 +3035,7 @@
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT14" t="n">
         <v>24</v>
@@ -2983,7 +3050,7 @@
         <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -3042,46 +3109,46 @@
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>86.2</v>
+        <v>85.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L15" t="n">
         <v>6.8</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O15" t="n">
-        <v>17.9</v>
+        <v>18.2</v>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0.746</v>
       </c>
       <c r="R15" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T15" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="W15" t="n">
         <v>7.3</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.6</v>
+        <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,13 +3187,13 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
         <v>23</v>
@@ -3135,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
         <v>9</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ15" t="n">
         <v>19</v>
@@ -3153,28 +3220,28 @@
         <v>19</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>7</v>
       </c>
       <c r="AW15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA15" t="n">
         <v>18</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>21</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -3209,37 +3276,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
         <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="H16" t="n">
         <v>48.9</v>
       </c>
       <c r="I16" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J16" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L16" t="n">
         <v>5.4</v>
       </c>
       <c r="M16" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O16" t="n">
         <v>18.5</v>
@@ -3248,19 +3315,19 @@
         <v>23.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.781</v>
+        <v>0.778</v>
       </c>
       <c r="R16" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S16" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T16" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U16" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V16" t="n">
         <v>13</v>
@@ -3275,19 +3342,19 @@
         <v>5.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,10 +3366,10 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
         <v>17</v>
@@ -3317,22 +3384,22 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
         <v>16</v>
@@ -3341,7 +3408,7 @@
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
@@ -3353,10 +3420,10 @@
         <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB16" t="n">
         <v>12</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>-3.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>18</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3538,13 +3605,13 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>29</v>
       </c>
       <c r="BC17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3660,7 +3727,7 @@
         <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
         <v>8</v>
@@ -3684,7 +3751,7 @@
         <v>4</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP18" t="n">
         <v>26</v>
@@ -3693,10 +3760,10 @@
         <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3711,16 +3778,16 @@
         <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
         <v>29</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -3755,58 +3822,58 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
         <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>0.216</v>
+        <v>0.2</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J19" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
         <v>5.1</v>
       </c>
       <c r="M19" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="N19" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O19" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P19" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.759</v>
+        <v>0.756</v>
       </c>
       <c r="R19" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S19" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T19" t="n">
         <v>40.8</v>
       </c>
       <c r="U19" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
         <v>15.1</v>
@@ -3815,10 +3882,10 @@
         <v>8.5</v>
       </c>
       <c r="X19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z19" t="n">
         <v>19.6</v>
@@ -3827,13 +3894,13 @@
         <v>21.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.5</v>
+        <v>97.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.6</v>
+        <v>-9</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,13 +3912,13 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3869,13 +3936,13 @@
         <v>4</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
@@ -3893,10 +3960,10 @@
         <v>7</v>
       </c>
       <c r="AX19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ19" t="n">
         <v>11</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -3937,67 +4004,67 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
         <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>0.52</v>
+        <v>0.529</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J20" t="n">
-        <v>83.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.455</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
         <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.761</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="S20" t="n">
         <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>44</v>
+        <v>44.3</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
         <v>7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
@@ -4006,28 +4073,28 @@
         <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
         <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG20" t="n">
         <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>10</v>
@@ -4036,7 +4103,7 @@
         <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>24</v>
@@ -4045,7 +4112,7 @@
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
@@ -4054,28 +4121,28 @@
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
         <v>17</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
         <v>29</v>
@@ -4087,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF21" t="n">
         <v>30</v>
@@ -4227,7 +4294,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4248,16 +4315,16 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
         <v>21</v>
       </c>
       <c r="AX21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY21" t="n">
         <v>6</v>
@@ -4266,7 +4333,7 @@
         <v>25</v>
       </c>
       <c r="BA21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -4301,61 +4368,61 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" t="n">
         <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J22" t="n">
-        <v>85</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L22" t="n">
         <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.321</v>
+        <v>0.32</v>
       </c>
       <c r="O22" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="P22" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="R22" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S22" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="T22" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
       <c r="U22" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W22" t="n">
         <v>7.3</v>
@@ -4364,25 +4431,25 @@
         <v>6</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z22" t="n">
         <v>22.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>100.1</v>
+        <v>99.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF22" t="n">
         <v>16</v>
@@ -4391,7 +4458,7 @@
         <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>14</v>
@@ -4409,10 +4476,10 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP22" t="n">
         <v>13</v>
@@ -4421,7 +4488,7 @@
         <v>18</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4433,7 +4500,7 @@
         <v>28</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW22" t="n">
         <v>19</v>
@@ -4442,19 +4509,19 @@
         <v>3</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ22" t="n">
         <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -4498,40 +4565,40 @@
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J23" t="n">
         <v>81.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
         <v>0.361</v>
       </c>
       <c r="O23" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="P23" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
         <v>20.6</v>
@@ -4540,25 +4607,25 @@
         <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.8</v>
+        <v>-6.1</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4582,7 +4649,7 @@
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>20</v>
@@ -4606,16 +4673,16 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV23" t="n">
         <v>23</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>24</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4624,13 +4691,13 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>19</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4779,7 +4846,7 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4806,7 +4873,7 @@
         <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>0.547</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
       <c r="J25" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L25" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="M25" t="n">
         <v>26.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.357</v>
+        <v>0.361</v>
       </c>
       <c r="O25" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P25" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R25" t="n">
         <v>10.6</v>
@@ -4898,19 +4965,19 @@
         <v>42.5</v>
       </c>
       <c r="U25" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V25" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="n">
         <v>22.2</v>
@@ -4919,25 +4986,25 @@
         <v>20.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.7</v>
+        <v>106.1</v>
       </c>
       <c r="AC25" t="n">
         <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI25" t="n">
         <v>3</v>
@@ -4955,10 +5022,10 @@
         <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
         <v>25</v>
@@ -4976,10 +5043,10 @@
         <v>19</v>
       </c>
       <c r="AU25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
@@ -5000,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F26" t="n">
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.673</v>
+        <v>0.667</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
@@ -5047,10 +5114,10 @@
         <v>38.4</v>
       </c>
       <c r="J26" t="n">
-        <v>86.3</v>
+        <v>86.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L26" t="n">
         <v>10.1</v>
@@ -5059,25 +5126,25 @@
         <v>27.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O26" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P26" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R26" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="S26" t="n">
         <v>34.9</v>
       </c>
       <c r="T26" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="U26" t="n">
         <v>22.3</v>
@@ -5101,16 +5168,16 @@
         <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.6</v>
+        <v>102.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5119,13 +5186,13 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -5140,7 +5207,7 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP26" t="n">
         <v>27</v>
@@ -5155,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="AT26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="n">
         <v>9</v>
@@ -5164,16 +5231,16 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>24</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" t="n">
         <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>0.36</v>
+        <v>0.347</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="K27" t="n">
         <v>0.451</v>
@@ -5238,37 +5305,37 @@
         <v>5.1</v>
       </c>
       <c r="M27" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N27" t="n">
         <v>0.326</v>
       </c>
       <c r="O27" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="P27" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.778</v>
+        <v>0.78</v>
       </c>
       <c r="R27" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S27" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T27" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V27" t="n">
         <v>16.4</v>
       </c>
       <c r="W27" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X27" t="n">
         <v>3.9</v>
@@ -5277,28 +5344,28 @@
         <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA27" t="n">
         <v>24.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.2</v>
+        <v>100.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
       <c r="AD27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF27" t="n">
         <v>22</v>
       </c>
-      <c r="AE27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>21</v>
-      </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>6</v>
@@ -5328,13 +5395,13 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
         <v>8</v>
@@ -5361,10 +5428,10 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -5396,34 +5463,34 @@
         <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H28" t="n">
         <v>48.9</v>
       </c>
       <c r="I28" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J28" t="n">
-        <v>83.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.453</v>
+        <v>0.457</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="M28" t="n">
         <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.364</v>
+        <v>0.37</v>
       </c>
       <c r="O28" t="n">
         <v>16.7</v>
@@ -5435,49 +5502,49 @@
         <v>0.764</v>
       </c>
       <c r="R28" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="S28" t="n">
         <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.4</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X28" t="n">
         <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>100.7</v>
+        <v>101.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
         <v>9</v>
@@ -5489,10 +5556,10 @@
         <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5504,46 +5571,46 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT28" t="n">
         <v>12</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>11</v>
       </c>
       <c r="AU28" t="n">
         <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA28" t="n">
         <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -5575,40 +5642,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F29" t="n">
         <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.673</v>
+        <v>0.667</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J29" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K29" t="n">
         <v>0.458</v>
       </c>
       <c r="L29" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="N29" t="n">
         <v>0.349</v>
       </c>
       <c r="O29" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P29" t="n">
         <v>25.5</v>
@@ -5617,19 +5684,19 @@
         <v>0.781</v>
       </c>
       <c r="R29" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S29" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U29" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W29" t="n">
         <v>7.4</v>
@@ -5638,25 +5705,25 @@
         <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA29" t="n">
         <v>21.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>105.8</v>
+        <v>106.2</v>
       </c>
       <c r="AC29" t="n">
         <v>4.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF29" t="n">
         <v>5</v>
@@ -5665,25 +5732,25 @@
         <v>5</v>
       </c>
       <c r="AH29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK29" t="n">
         <v>9</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AL29" t="n">
         <v>8</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>9</v>
-      </c>
       <c r="AM29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5710,10 +5777,10 @@
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
@@ -5844,7 +5911,7 @@
         <v>25</v>
       </c>
       <c r="AG30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5883,7 +5950,7 @@
         <v>25</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>27</v>
@@ -5895,7 +5962,7 @@
         <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>9</v>
@@ -6029,7 +6096,7 @@
         <v>10</v>
       </c>
       <c r="AH31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6038,7 +6105,7 @@
         <v>20</v>
       </c>
       <c r="AK31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6065,7 +6132,7 @@
         <v>9</v>
       </c>
       <c r="AT31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU31" t="n">
         <v>6</v>
@@ -6074,7 +6141,7 @@
         <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX31" t="n">
         <v>14</v>
@@ -6089,7 +6156,7 @@
         <v>17</v>
       </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-8-2014-15</t>
+          <t>2015-02-08</t>
         </is>
       </c>
     </row>
